--- a/artfynd/A 27734-2023 artfynd.xlsx
+++ b/artfynd/A 27734-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 27734-2023 artfynd.xlsx
+++ b/artfynd/A 27734-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -929,6 +929,130 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>120230534</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57744</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>102999</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Björktrast</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Turdus pilaris</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Tjärnbergskorset, Bränslan, Stöde, Mpd</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>581016</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6919400</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Bodil Eriksson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Bodil Eriksson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 27734-2023 artfynd.xlsx
+++ b/artfynd/A 27734-2023 artfynd.xlsx
@@ -934,7 +934,7 @@
         <v>120230534</v>
       </c>
       <c r="B4" t="n">
-        <v>57744</v>
+        <v>57754</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 27734-2023 artfynd.xlsx
+++ b/artfynd/A 27734-2023 artfynd.xlsx
@@ -675,42 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>114849639</v>
+        <v>116118780</v>
       </c>
       <c r="B2" t="n">
-        <v>57885</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57247</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103042</v>
+        <v>100038</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -761,22 +756,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-04-20</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-04-20</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -803,32 +798,27 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>116118780</v>
+        <v>120230534</v>
       </c>
       <c r="B3" t="n">
-        <v>56577</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58393</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100038</v>
+        <v>102999</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skogsduva</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Columba oenas</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -838,21 +828,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Tjärnbergskorset, Bränslan, Stöde, Mpd</t>
@@ -889,22 +875,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-04-20</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-04-20</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -931,52 +917,51 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120230534</v>
+        <v>114849639</v>
       </c>
       <c r="B4" t="n">
-        <v>57754</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58602</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102999</v>
+        <v>103042</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Tjärnbergskorset, Bränslan, Stöde, Mpd</t>
@@ -1013,22 +998,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 27734-2023 artfynd.xlsx
+++ b/artfynd/A 27734-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -795,6 +800,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116118780</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -914,6 +924,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120230534</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1037,8 +1052,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114849639</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>